--- a/artfynd/A 14731-2026 artfynd.xlsx
+++ b/artfynd/A 14731-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,59 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>62130308</v>
+        <v>62130307</v>
       </c>
       <c r="B2" t="n">
-        <v>90674</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92699</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5964</v>
+        <v>366</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Pers.) Jülich</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Lenåsen, Gstr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>590190.156936113</v>
+        <v>590189</v>
       </c>
       <c r="R2" t="n">
-        <v>6739913.958145214</v>
+        <v>6739995</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -757,39 +743,31 @@
           <t>2016-09-22</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2016-09-22</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>stora ringar</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>grov lågörtsgranskog</t>
+          <t>grov rik granskog</t>
+        </is>
+      </c>
+      <c r="AN2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>1 substratenheter # äldre asplåga</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -807,37 +785,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>62130310</v>
+        <v>62130304</v>
       </c>
       <c r="B3" t="n">
-        <v>85253</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87196</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1988</v>
+        <v>427</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kryddspindling</t>
+          <t>Puderspindling</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cortinarius percomis</t>
+          <t>Cortinarius aureopulverulentus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -856,10 +829,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>590237.9435506256</v>
+        <v>590119</v>
       </c>
       <c r="R3" t="n">
-        <v>6739881.941616332</v>
+        <v>6739906</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,21 +862,11 @@
           <t>2016-09-22</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2016-09-22</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -915,7 +878,12 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>örtrik, grov granskog</t>
+          <t>grov äldre lågörtsgranskog</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>barrmatta</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -933,37 +901,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>62130309</v>
+        <v>62130311</v>
       </c>
       <c r="B4" t="n">
-        <v>90665</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87300</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4366</v>
+        <v>454</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Rovspindling</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Cortinarius napus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -982,10 +945,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>590188.0814154308</v>
+        <v>590275</v>
       </c>
       <c r="R4" t="n">
-        <v>6739899.248611812</v>
+        <v>6739861</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1015,19 +978,14 @@
           <t>2016-09-22</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2016-09-22</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>bild kollad med Karl Soop, ljust köttröd hatt, ej KOH-reaktion utom ljusblå! på bulb, vitt kött, ljust bruna skivor, ej doft</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1041,7 +999,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>äldre kalkpåverkad granskog</t>
+          <t>grov lågörtsgranskog med gråal</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1059,59 +1017,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>62130305</v>
+        <v>62817725</v>
       </c>
       <c r="B5" t="n">
-        <v>88853</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4189</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kamjordstjärna</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Geastrum pectinatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Lenåsen, Gstr</t>
+          <t>Lenåsens sydöstra delar, Gstr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>590142.9254575691</v>
+        <v>590136</v>
       </c>
       <c r="R5" t="n">
-        <v>6739924.003448655</v>
+        <v>6739930</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1138,22 +1082,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2016-09-22</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-04-26</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2016-09-22</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-04-26</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1167,12 +1101,15 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>grov lågörtsgranskog</t>
-        </is>
+          <t>gammal grov kalkgranskog</t>
+        </is>
+      </c>
+      <c r="AN5" t="n">
+        <v>2</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>barrmatta</t>
+          <t>2 substratenheter # grov granlåga</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1190,48 +1127,48 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>91461415</v>
+        <v>62817727</v>
       </c>
       <c r="B6" t="n">
-        <v>100847</v>
+        <v>91909</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Lennåsen, 200 möh, Gstr</t>
+          <t>Lenåsens sydöstra delar, Gstr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>590238</v>
+        <v>590197</v>
       </c>
       <c r="R6" t="n">
-        <v>6739954</v>
+        <v>6740014</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1255,12 +1192,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2001-09-28</t>
+          <t>2016-04-26</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2001-09-28</t>
+          <t>2016-04-26</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1274,26 +1211,819 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>skog, Granskog, grov ca 100årig, örtrik granskog på strandvall nedom Hk</t>
-        </is>
-      </c>
-      <c r="AR6" t="inlineStr">
-        <is>
-          <t>Gst Fyndnr 243017N</t>
+          <t>grov gammal granskog</t>
+        </is>
+      </c>
+      <c r="AN6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>1 substratenheter # granlåga</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>62130310</v>
+      </c>
+      <c r="B7" t="n">
+        <v>87322</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>1988</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Kryddspindling</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Cortinarius percomis</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Lenåsen, Gstr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>590238</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6739882</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Ockelbo</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Ockelbo</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2016-09-22</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2016-09-22</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>örtrik, grov granskog</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>62130305</v>
+      </c>
+      <c r="B8" t="n">
+        <v>91330</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>4189</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Kamjordstjärna</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Geastrum pectinatum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Pers., nom.sanct</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Lenåsen, Gstr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>590143</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6739924</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Ockelbo</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Ockelbo</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2016-09-22</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2016-09-22</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>grov lågörtsgranskog</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>barrmatta</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>62130303</v>
+      </c>
+      <c r="B9" t="n">
+        <v>93209</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Lenåsen, Gstr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>590121</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6739905</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Ockelbo</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Ockelbo</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2016-09-22</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2016-09-22</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>grov granskog</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>barrmatta</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>62130309</v>
+      </c>
+      <c r="B10" t="n">
+        <v>93209</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Lenåsen, Gstr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>590188</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6739899</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Ockelbo</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Ockelbo</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2016-09-22</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2016-09-22</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>äldre kalkpåverkad granskog</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>62130302</v>
+      </c>
+      <c r="B11" t="n">
+        <v>93233</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Lenåsen, Gstr</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>590126</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6739925</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Ockelbo</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Ockelbo</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2016-09-22</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2016-09-22</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>grov äldre lågörtsgranskog</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>62130308</v>
+      </c>
+      <c r="B12" t="n">
+        <v>93233</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Lenåsen, Gstr</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>590190</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6739914</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Ockelbo</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Ockelbo</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2016-09-22</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2016-09-22</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>stora ringar</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>grov lågörtsgranskog</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>91461415</v>
+      </c>
+      <c r="B13" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Lennåsen, 200 möh, Gstr</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>590238</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6739954</v>
+      </c>
+      <c r="S13" t="n">
+        <v>25</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Ockelbo</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Ockelbo</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2001-09-28</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2001-09-28</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>skog, Granskog, grov ca 100årig, örtrik granskog på strandvall nedom Hk</t>
+        </is>
+      </c>
+      <c r="AR13" t="inlineStr">
+        <is>
+          <t>Gst Fyndnr 243017N</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
           <t>Peter Ståhl</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
+      <c r="AX13" t="inlineStr">
         <is>
           <t>Peter Ståhl</t>
         </is>
       </c>
-      <c r="AY6" t="inlineStr">
+      <c r="AY13" t="inlineStr">
         <is>
           <t>Gästriklands flora (2016)</t>
         </is>
